--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -408,7 +408,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>量を理解し、表現する方法。 / How the Quantity should be understood and represented.</t>
+    <t>数量の評価解釈コード / How the Quantity should be understood and represented.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
@@ -528,7 +528,7 @@
     <t>Ratio.denominator.comparator</t>
   </si>
   <si>
-    <t>&lt;|&lt;= |&gt; = |&gt;  - 価値を理解する方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+    <t>&lt;|&lt;= |&gt; = |&gt;  - 値の比較方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
   </si>
   <si>
     <t>値をどのように理解し、表現する必要があるか - 測定の問題により実際の値が記載されている値よりも大きいか小さいかどうか。例えばコンパレータが「&lt;」の場合、実際の値は&lt;stated値です。 / How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
@@ -904,7 +904,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="70.171875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="66.87109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="57.89453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>
